--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,8 +786,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108719960</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108719960</v>
+        <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogsväg mot St Örtjärn Väster, Mattjärn, Lindome, Hl</t>
+          <t>Granndalen Väst, Granndalen Väst, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334732</v>
+        <v>334646</v>
       </c>
       <c r="R2" t="n">
-        <v>6386927</v>
+        <v>6387026</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,6 +785,120 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135744747</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>108719960</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogsväg mot St Örtjärn Väster, Mattjärn, Lindome, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>334732</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6386927</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/108719960</t>
         </is>
@@ -795,6 +907,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23796-2026 artfynd.xlsx
+++ b/artfynd/A 23796-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744747</v>
       </c>
       <c r="B2" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
